--- a/Design/Datas/行为表.xlsx
+++ b/Design/Datas/行为表.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rcdb4ff0dd75f49e0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R6972fdce52b741e0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -326,6 +326,18 @@
         <x:v>{播放演出脚本,1}</x:v>
       </x:c>
     </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="1"/>
+      <x:c r="B6" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="str">
+        <x:v>标记测试剧情完成</x:v>
+      </x:c>
+      <x:c r="D6" s="1" t="str">
+        <x:v>{设置游戏布尔变量,1,true}</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
